--- a/Entity Relationship Diagram.xlsx
+++ b/Entity Relationship Diagram.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1332a08b4347893b/Desktop/MSc Health Data Science/Assignment 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="8_{BB03E1D3-2253-4E07-811B-71B0DC0D4BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{144B9F37-FC75-493A-9E85-BA4B6C7A6855}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="8_{BB03E1D3-2253-4E07-811B-71B0DC0D4BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A97B38E0-D21C-4545-AF7C-A4A090612B71}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{185AF615-FE68-4665-96DF-946565C507AA}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="14400" windowHeight="8170" xr2:uid="{185AF615-FE68-4665-96DF-946565C507AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Relationships" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="64">
   <si>
     <t>Hospitals</t>
   </si>
@@ -209,6 +209,30 @@
   </si>
   <si>
     <t>Date prescribed</t>
+  </si>
+  <si>
+    <t>Relationships:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital </t>
+  </si>
+  <si>
+    <t>Doctor</t>
+  </si>
+  <si>
+    <t>One-to-many</t>
+  </si>
+  <si>
+    <t>Patient</t>
+  </si>
+  <si>
+    <t>Doctor:</t>
+  </si>
+  <si>
+    <t>Patient:</t>
+  </si>
+  <si>
+    <t>Prescription:</t>
   </si>
 </sst>
 </file>
@@ -252,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -278,6 +302,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -300,22 +330,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>34925</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>23813</xdr:rowOff>
+      <xdr:colOff>144600</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>62821</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>555625</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>165102</xdr:rowOff>
+      <xdr:colOff>499453</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>181106</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Left Brace 2">
+        <xdr:cNvPr id="6" name="Arrow: Right 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36865638-4B28-1E06-5655-29487ADB35E2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69DFDED3-A7BD-5F8C-0CE4-8ED9CAF21A76}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -323,25 +353,27 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="644525" y="576263"/>
-          <a:ext cx="520700" cy="141289"/>
+          <a:off x="1077858" y="428427"/>
+          <a:ext cx="354853" cy="118285"/>
         </a:xfrm>
-        <a:prstGeom prst="leftBrace">
+        <a:prstGeom prst="rightArrow">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
         </a:lnRef>
-        <a:fillRef idx="0">
+        <a:fillRef idx="1">
           <a:schemeClr val="accent1"/>
         </a:fillRef>
-        <a:effectRef idx="1">
+        <a:effectRef idx="0">
           <a:schemeClr val="accent1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
+          <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -358,22 +390,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>33338</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>22225</xdr:rowOff>
+      <xdr:colOff>144318</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38485</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>554038</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>168277</xdr:rowOff>
+      <xdr:colOff>499171</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>156770</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Left Brace 10">
+        <xdr:cNvPr id="8" name="Arrow: Right 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25C42F85-B153-458D-BBA7-DB37F2CDA4CF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ACB6901-2127-4350-A7E7-069E90767E51}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -381,57 +413,35 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="642938" y="758825"/>
-          <a:ext cx="520700" cy="146052"/>
+          <a:off x="1077576" y="625379"/>
+          <a:ext cx="354853" cy="118285"/>
         </a:xfrm>
-        <a:prstGeom prst="leftBrace">
+        <a:prstGeom prst="rightArrow">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="156082"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:effectLst/>
       </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:endParaRPr kumimoji="0" lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:uLnTx/>
-            <a:uFillTx/>
-            <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -440,22 +450,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>33337</xdr:colOff>
+      <xdr:colOff>136681</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>20637</xdr:rowOff>
+      <xdr:rowOff>37018</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>554037</xdr:colOff>
+      <xdr:colOff>491534</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>161926</xdr:rowOff>
+      <xdr:rowOff>155303</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="Left Brace 15">
+        <xdr:cNvPr id="18" name="Arrow: Right 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8DD0273-F5A4-48D4-B8AA-D2CB1E5F035A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F4E281B-896A-4CC0-BEBA-8330BF7D5E92}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -463,57 +473,35 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="642937" y="941387"/>
-          <a:ext cx="520700" cy="141289"/>
+          <a:off x="1070672" y="999484"/>
+          <a:ext cx="354853" cy="118285"/>
         </a:xfrm>
-        <a:prstGeom prst="leftBrace">
+        <a:prstGeom prst="rightArrow">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="156082"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:effectLst/>
       </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:endParaRPr kumimoji="0" lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:uLnTx/>
-            <a:uFillTx/>
-            <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -521,81 +509,59 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>46038</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>22225</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>142377</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>34170</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>566738</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>163514</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>497230</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>152455</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="Left Brace 18">
+        <xdr:cNvPr id="20" name="Arrow: Right 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DFA1891-0F62-410F-BF64-DAB2B12A9770}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01783C43-C537-42CE-AF90-984931681438}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="10800000">
-          <a:off x="2058988" y="942975"/>
-          <a:ext cx="520700" cy="141289"/>
+        <a:xfrm>
+          <a:off x="1076368" y="811547"/>
+          <a:ext cx="354853" cy="118285"/>
         </a:xfrm>
-        <a:prstGeom prst="leftBrace">
+        <a:prstGeom prst="rightArrow">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="156082"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:effectLst/>
       </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:endParaRPr kumimoji="0" lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:uLnTx/>
-            <a:uFillTx/>
-            <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1314,42 +1280,69 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F3847A-C4F5-45B2-8224-604B11A41663}">
-  <dimension ref="A4:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="4"/>
-    <col min="3" max="3" width="11.36328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>2</v>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" s="9" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Entity Relationship Diagram.xlsx
+++ b/Entity Relationship Diagram.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1332a08b4347893b/Desktop/MSc Health Data Science/Assignment 1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1332a08b4347893b/Desktop/MSc Health Data Science/Assessment 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="250" documentId="8_{BB03E1D3-2253-4E07-811B-71B0DC0D4BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A97B38E0-D21C-4545-AF7C-A4A090612B71}"/>
+  <xr:revisionPtr revIDLastSave="262" documentId="8_{BB03E1D3-2253-4E07-811B-71B0DC0D4BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D484E30F-4259-4A4D-8503-8E1E0970D19F}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="14400" windowHeight="8170" xr2:uid="{185AF615-FE68-4665-96DF-946565C507AA}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{185AF615-FE68-4665-96DF-946565C507AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Relationships" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="56">
   <si>
     <t>Hospitals</t>
   </si>
@@ -118,75 +118,39 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Address</t>
-  </si>
-  <si>
     <t>Beds</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>Accreditation</t>
   </si>
   <si>
     <t>VARCHAR(100)</t>
   </si>
   <si>
-    <t>VARCHAR(200)</t>
-  </si>
-  <si>
     <t>INT</t>
   </si>
   <si>
-    <t>VARCHAR(50)</t>
-  </si>
-  <si>
-    <t>CHAR(1)</t>
-  </si>
-  <si>
     <t>Hospital name</t>
   </si>
   <si>
-    <t>Hospital type</t>
-  </si>
-  <si>
-    <t>Street address</t>
-  </si>
-  <si>
     <t>Number of beds</t>
   </si>
   <si>
-    <t>Y/N accreditation flag</t>
-  </si>
-  <si>
-    <t>Specialty</t>
-  </si>
-  <si>
     <t>INT FOREIGN KEY</t>
   </si>
   <si>
     <t>Doctor's name</t>
   </si>
   <si>
-    <t>Area of expertise</t>
-  </si>
-  <si>
     <t>Links to Hospitals</t>
   </si>
   <si>
     <t>DOB</t>
   </si>
   <si>
-    <t>Gender</t>
-  </si>
-  <si>
     <t>DATE</t>
   </si>
   <si>
-    <t>M/F</t>
-  </si>
-  <si>
     <t>Date of birth</t>
   </si>
   <si>
@@ -233,6 +197,18 @@
   </si>
   <si>
     <t>Prescription:</t>
+  </si>
+  <si>
+    <t>VARCHAR(20)</t>
+  </si>
+  <si>
+    <t>Accreditation status</t>
+  </si>
+  <si>
+    <t>Links to Doctor</t>
+  </si>
+  <si>
+    <t>Hospital</t>
   </si>
 </sst>
 </file>
@@ -978,7 +954,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748CCEA2-EACA-4859-A214-15B31AFA5B8B}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" style="4" customWidth="1"/>
@@ -987,7 +963,7 @@
     <col min="4" max="4" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1001,9 +977,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="7" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" s="7" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>6</v>
@@ -1015,263 +991,212 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="5" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
       <c r="B7" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="5" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="9" spans="1:9" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:9" s="7" customFormat="1" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="5" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="5" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="1:6" s="7" customFormat="1" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
-      <c r="B18" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1290,7 +1215,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1298,46 +1223,46 @@
     </row>
     <row r="3" spans="1:4" s="9" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
